--- a/output/chart_sales.xlsx
+++ b/output/chart_sales.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Месяц</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Февраль</t>
-  </si>
-  <si>
-    <t>Март</t>
   </si>
 </sst>
 </file>
@@ -110,35 +107,29 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Данные!$A$2:$A$4</c:f>
+              <c:f>Данные!$A$2:$A$3</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>Январь</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Февраль</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>Март</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Данные!$B$2:$B$4</c:f>
+              <c:f>Данные!$B$2:$B$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>150</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>200</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -508,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -535,14 +526,6 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>200</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
